--- a/data/patientinfo.xlsx
+++ b/data/patientinfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4398d374dcf79238/Desktop/eeg-viz/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{9CBF4047-2382-4732-99E5-84E5BF404058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03AD1FBE-471B-448B-939E-B355286491A3}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{9CBF4047-2382-4732-99E5-84E5BF404058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D647E5D9-8617-4468-B94C-69372BC9CFC3}"/>
   <bookViews>
-    <workbookView xWindow="-15825" yWindow="4020" windowWidth="17280" windowHeight="8925" xr2:uid="{54BE6250-3488-4FEB-933B-EC42D0A59200}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="11904" xr2:uid="{54BE6250-3488-4FEB-933B-EC42D0A59200}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="78">
   <si>
     <t>Age</t>
   </si>
@@ -228,6 +228,51 @@
   </si>
   <si>
     <t>Carn</t>
+  </si>
+  <si>
+    <t>DD</t>
+  </si>
+  <si>
+    <t>JS</t>
+  </si>
+  <si>
+    <t>KA</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>BH</t>
+  </si>
+  <si>
+    <t>VH</t>
+  </si>
+  <si>
+    <t>MiM</t>
+  </si>
+  <si>
+    <t>AOr</t>
+  </si>
+  <si>
+    <t>Tics</t>
+  </si>
+  <si>
+    <t>ADD</t>
+  </si>
+  <si>
+    <t>Migraines</t>
+  </si>
+  <si>
+    <t>Febrile sz</t>
+  </si>
+  <si>
+    <t>Syncope</t>
+  </si>
+  <si>
+    <t>Headaches</t>
+  </si>
+  <si>
+    <t>NA Control Group</t>
   </si>
 </sst>
 </file>
@@ -280,6 +325,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -599,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5C17194-6E25-4B02-8EC7-4EEE8B0DFDB2}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1082,6 +1131,142 @@
         <v>42</v>
       </c>
     </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="D28" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>30</v>
+      </c>
+      <c r="F32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34">
+        <v>10</v>
+      </c>
+      <c r="D34" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
